--- a/data/trans_orig/ESTUDIOS-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2007</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>25601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34952</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59411</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65233</t>
+          <t>67190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101162</t>
+          <t>100241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357769</t>
+          <t>357365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395053</t>
+          <t>394532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339321</t>
+          <t>336953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373259</t>
+          <t>373194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>705210</t>
+          <t>706751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758331</t>
+          <t>758465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65715</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98184</t>
+          <t>99868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52316</t>
+          <t>52111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80573</t>
+          <t>79736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>123323</t>
+          <t>126184</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168090</t>
+          <t>169346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169838</t>
+          <t>170020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219067</t>
+          <t>218843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164484</t>
+          <t>163213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208270</t>
+          <t>208660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343373</t>
+          <t>346960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411237</t>
+          <t>410428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423865</t>
+          <t>425093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>480358</t>
+          <t>481745</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>348091</t>
+          <t>349616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>397422</t>
+          <t>400970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>793944</t>
+          <t>791615</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>869455</t>
+          <t>865421</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70860</t>
+          <t>69816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107233</t>
+          <t>107863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50270</t>
+          <t>51401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85591</t>
+          <t>83000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129863</t>
+          <t>130217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178210</t>
+          <t>180117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117639</t>
+          <t>120108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160643</t>
+          <t>162046</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108688</t>
+          <t>108714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151478</t>
+          <t>154457</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>237864</t>
+          <t>237364</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>298173</t>
+          <t>295850</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>351407</t>
+          <t>352038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>402101</t>
+          <t>401299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>400065</t>
+          <t>401178</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>453041</t>
+          <t>453383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>766941</t>
+          <t>767364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>839385</t>
+          <t>840909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105331</t>
+          <t>103205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147201</t>
+          <t>143480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113491</t>
+          <t>113374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156127</t>
+          <t>154030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>229002</t>
+          <t>230392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>285860</t>
+          <t>291376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80099</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119824</t>
+          <t>120034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46655</t>
+          <t>46502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>75408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138275</t>
+          <t>139487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>183975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245350</t>
+          <t>245592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290790</t>
+          <t>291635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235237</t>
+          <t>240355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>283268</t>
+          <t>283475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>499389</t>
+          <t>498621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>561307</t>
+          <t>563433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>129952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172858</t>
+          <t>172360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>171836</t>
+          <t>174178</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216360</t>
+          <t>216500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,47 +2377,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>41,99%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>344800</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>310084</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>376674</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>33,32%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>344800</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>316502</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>376283</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58644</t>
+          <t>58763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19507</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41498</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59482</t>
+          <t>57243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92653</t>
+          <t>90125</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>110459</t>
+          <t>108630</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>148931</t>
+          <t>147936</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>88043</t>
+          <t>86610</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>122087</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>205832</t>
+          <t>210525</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>260777</t>
+          <t>261391</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193422</t>
+          <t>193198</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232268</t>
+          <t>232488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>249597</t>
+          <t>249951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>288959</t>
+          <t>287216</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>457029</t>
+          <t>455208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>512320</t>
+          <t>510494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>40136</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>33045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61374</t>
+          <t>61626</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47801</t>
+          <t>48399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75580</t>
+          <t>75969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54797</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88064</t>
+          <t>88157</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124106</t>
+          <t>123775</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>186525</t>
+          <t>186004</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>220393</t>
+          <t>217188</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268440</t>
+          <t>267987</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>295625</t>
+          <t>295231</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>461951</t>
+          <t>464548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>504939</t>
+          <t>505348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38231</t>
+          <t>37530</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30749</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>61815</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>157806</t>
+          <t>157434</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180619</t>
+          <t>180756</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>292539</t>
+          <t>291469</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>314783</t>
+          <t>315380</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>456484</t>
+          <t>457607</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>489271</t>
+          <t>490837</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>504486</t>
+          <t>509292</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>593968</t>
+          <t>600239</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>438292</t>
+          <t>438952</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>520395</t>
+          <t>516263</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>973294</t>
+          <t>966748</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1091586</t>
+          <t>1094736</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1635903</t>
+          <t>1627685</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1751126</t>
+          <t>1750356</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1529325</t>
+          <t>1530722</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1646395</t>
+          <t>1646221</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3190490</t>
+          <t>3194336</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3359739</t>
+          <t>3362410</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>973795</t>
+          <t>983225</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1084056</t>
+          <t>1088008</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1254028</t>
+          <t>1252523</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1366719</t>
+          <t>1367276</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2267662</t>
+          <t>2259779</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2423993</t>
+          <t>2412654</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2012</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>39316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67341</t>
+          <t>66416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53191</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85895</t>
+          <t>86347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364640</t>
+          <t>363795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396071</t>
+          <t>395194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323579</t>
+          <t>322136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357877</t>
+          <t>356569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697348</t>
+          <t>697719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744095</t>
+          <t>744859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42505</t>
+          <t>43339</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71536</t>
+          <t>71350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26947</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76789</t>
+          <t>76313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113660</t>
+          <t>114428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152430</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199540</t>
+          <t>195029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147019</t>
+          <t>146897</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191003</t>
+          <t>190481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>307745</t>
+          <t>309366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>373306</t>
+          <t>376496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419197</t>
+          <t>421187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>468943</t>
+          <t>472733</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>346458</t>
+          <t>346021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>394064</t>
+          <t>395803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>783336</t>
+          <t>779992</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>854894</t>
+          <t>854189</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83564</t>
+          <t>82456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54578</t>
+          <t>54349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88669</t>
+          <t>87994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115101</t>
+          <t>114568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159618</t>
+          <t>160283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97158</t>
+          <t>96537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>139512</t>
+          <t>138188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93867</t>
+          <t>94539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134319</t>
+          <t>134208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>201831</t>
+          <t>199391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>259900</t>
+          <t>259508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>424077</t>
+          <t>420570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>474076</t>
+          <t>474481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>430974</t>
+          <t>432980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>485583</t>
+          <t>484332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>869834</t>
+          <t>871213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>943212</t>
+          <t>946507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94823</t>
+          <t>94938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134138</t>
+          <t>137438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119729</t>
+          <t>118551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163096</t>
+          <t>162064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226392</t>
+          <t>224555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284770</t>
+          <t>284327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87382</t>
+          <t>89057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129094</t>
+          <t>129994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70733</t>
+          <t>70854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108016</t>
+          <t>110527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>169753</t>
+          <t>169625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225189</t>
+          <t>226859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345977</t>
+          <t>346105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>396049</t>
+          <t>396637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>310874</t>
+          <t>312037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363724</t>
+          <t>364025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>669794</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>741899</t>
+          <t>744646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115770</t>
+          <t>115944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156718</t>
+          <t>158420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>167580</t>
+          <t>165677</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>218007</t>
+          <t>214601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>298065</t>
+          <t>296351</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>360931</t>
+          <t>358605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41456</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71846</t>
+          <t>74518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>173871</t>
+          <t>175520</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>218260</t>
+          <t>221176</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>146865</t>
+          <t>146057</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188577</t>
+          <t>188508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>331704</t>
+          <t>336056</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>393939</t>
+          <t>397121</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167143</t>
+          <t>167463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210733</t>
+          <t>210706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>242687</t>
+          <t>241509</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>285240</t>
+          <t>286279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>424833</t>
+          <t>418290</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>485265</t>
+          <t>481146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>51149</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68382</t>
+          <t>67695</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101785</t>
+          <t>100951</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>41295</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>69406</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118333</t>
+          <t>118621</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>164764</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>184137</t>
+          <t>185471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>220496</t>
+          <t>222044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>266936</t>
+          <t>268532</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>298158</t>
+          <t>299711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>462216</t>
+          <t>460837</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>510697</t>
+          <t>509807</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>24359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>48078</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>39939</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>46845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79455</t>
+          <t>80207</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>199018</t>
+          <t>197851</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222164</t>
+          <t>221852</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>337581</t>
+          <t>337131</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>361073</t>
+          <t>362148</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>543587</t>
+          <t>542708</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>580138</t>
+          <t>577003</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>435808</t>
+          <t>441643</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>520932</t>
+          <t>524800</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>418653</t>
+          <t>416935</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>497333</t>
+          <t>497515</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>879508</t>
+          <t>883662</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1000252</t>
+          <t>1003061</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1905733</t>
+          <t>1904778</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2025050</t>
+          <t>2023077</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1696621</t>
+          <t>1699465</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1815997</t>
+          <t>1818182</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3635073</t>
+          <t>3635571</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3803877</t>
+          <t>3806724</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>925115</t>
+          <t>919538</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1030407</t>
+          <t>1034254</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1275324</t>
+          <t>1276796</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1390487</t>
+          <t>1394574</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2236082</t>
+          <t>2228586</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2391923</t>
+          <t>2393811</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2016</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>30681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55001</t>
+          <t>55217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59846</t>
+          <t>58224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69397</t>
+          <t>70314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>106488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329662</t>
+          <t>326616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359769</t>
+          <t>358171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305978</t>
+          <t>308418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336244</t>
+          <t>337607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>645578</t>
+          <t>645415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689099</t>
+          <t>688910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>36693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40262</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67049</t>
+          <t>67005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113302</t>
+          <t>112547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154443</t>
+          <t>155201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143664</t>
+          <t>142952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>185262</t>
+          <t>184302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264313</t>
+          <t>267042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322767</t>
+          <t>324077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>364161</t>
+          <t>364356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>409553</t>
+          <t>411182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>331297</t>
+          <t>331501</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>374324</t>
+          <t>377051</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>709432</t>
+          <t>709320</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>774415</t>
+          <t>771855</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50140</t>
+          <t>48999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80567</t>
+          <t>82511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33420</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58437</t>
+          <t>60309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91728</t>
+          <t>92680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130575</t>
+          <t>132107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129936</t>
+          <t>130980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>175379</t>
+          <t>176377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137330</t>
+          <t>136720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181293</t>
+          <t>182200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>279659</t>
+          <t>282433</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>341087</t>
+          <t>340515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>411515</t>
+          <t>409936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>462125</t>
+          <t>461621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>411953</t>
+          <t>412854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>458631</t>
+          <t>459356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>838075</t>
+          <t>836788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>908269</t>
+          <t>904797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63846</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96573</t>
+          <t>96574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50899</t>
+          <t>49413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79662</t>
+          <t>78725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119626</t>
+          <t>119734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163235</t>
+          <t>165082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80999</t>
+          <t>80737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121251</t>
+          <t>120293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84852</t>
+          <t>86779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124052</t>
+          <t>125121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176196</t>
+          <t>175814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229000</t>
+          <t>231057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>428710</t>
+          <t>429780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>478560</t>
+          <t>477438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392613</t>
+          <t>390196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445634</t>
+          <t>439490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835313</t>
+          <t>835689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>906900</t>
+          <t>907985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73966</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>110236</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105128</t>
+          <t>104934</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145892</t>
+          <t>146570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>192704</t>
+          <t>189412</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>247455</t>
+          <t>246079</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62528</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99582</t>
+          <t>99078</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>59422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105101</t>
+          <t>102572</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149891</t>
+          <t>148974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>237844</t>
+          <t>236712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>281784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245281</t>
+          <t>247202</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>291950</t>
+          <t>292522</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>498697</t>
+          <t>495786</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>561742</t>
+          <t>560423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118325</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158393</t>
+          <t>157993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159384</t>
+          <t>159124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203378</t>
+          <t>203579</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>287566</t>
+          <t>286458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>348567</t>
+          <t>348725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14936</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34358</t>
+          <t>34673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39625</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>69855</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117357</t>
+          <t>116958</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152488</t>
+          <t>153407</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99115</t>
+          <t>99018</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134889</t>
+          <t>135312</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>226447</t>
+          <t>223869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277790</t>
+          <t>276309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150402</t>
+          <t>149710</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187102</t>
+          <t>186742</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>217666</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254806</t>
+          <t>257575</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>380566</t>
+          <t>379888</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>433237</t>
+          <t>434065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20810</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47406</t>
+          <t>47521</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72926</t>
+          <t>71775</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54468</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89622</t>
+          <t>90817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>108052</t>
+          <t>110328</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>152249</t>
+          <t>154192</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>170142</t>
+          <t>171384</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196099</t>
+          <t>197451</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>297724</t>
+          <t>295282</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>334736</t>
+          <t>337115</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>478458</t>
+          <t>475738</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>523694</t>
+          <t>522919</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>503587</t>
+          <t>505598</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>592799</t>
+          <t>592706</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>504970</t>
+          <t>503545</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>597590</t>
+          <t>590770</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1037197</t>
+          <t>1043913</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1157595</t>
+          <t>1163837</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2024470</t>
+          <t>2019681</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2136866</t>
+          <t>2137122</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1929646</t>
+          <t>1927529</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2051783</t>
+          <t>2048841</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3973205</t>
+          <t>3989228</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4138121</t>
+          <t>4149508</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>708414</t>
+          <t>701210</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>801609</t>
+          <t>799716</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>940730</t>
+          <t>939460</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1055023</t>
+          <t>1053606</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1677152</t>
+          <t>1675399</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1822310</t>
+          <t>1818983</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2023</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57157</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27841</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58737</t>
+          <t>58124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56295</t>
+          <t>56402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101978</t>
+          <t>102281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327022</t>
+          <t>331448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>368631</t>
+          <t>370172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239888</t>
+          <t>240493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276130</t>
+          <t>275463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582736</t>
+          <t>583732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>636520</t>
+          <t>635880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>45357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72802</t>
+          <t>69549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118985</t>
+          <t>115268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84124</t>
+          <t>89099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175240</t>
+          <t>174413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175347</t>
+          <t>177236</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>271736</t>
+          <t>268535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>268188</t>
+          <t>269934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>318030</t>
+          <t>320040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>318700</t>
+          <t>318919</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>418029</t>
+          <t>413984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>607877</t>
+          <t>611128</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>716495</t>
+          <t>715996</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48650</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25873</t>
+          <t>26498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33611</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69088</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122684</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164986</t>
+          <t>167457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130785</t>
+          <t>128841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164611</t>
+          <t>163207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>264060</t>
+          <t>266686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>319640</t>
+          <t>321273</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>330721</t>
+          <t>328999</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>374549</t>
+          <t>373354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>348556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>383060</t>
+          <t>384406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>689618</t>
+          <t>688572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>748187</t>
+          <t>745477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52165</t>
+          <t>53089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21946</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38373</t>
+          <t>39215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54415</t>
+          <t>53120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>82333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>67598</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>233705</t>
+          <t>234496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138267</t>
+          <t>140521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189513</t>
+          <t>187540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193069</t>
+          <t>213780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>404129</t>
+          <t>403660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>573220</t>
+          <t>573172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>786404</t>
+          <t>792695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451511</t>
+          <t>451791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>512012</t>
+          <t>512688</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1051654</t>
+          <t>1045657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1331913</t>
+          <t>1312225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83000</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53141</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90034</t>
+          <t>88385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73581</t>
+          <t>74982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>152259</t>
+          <t>156803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90530</t>
+          <t>90706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126063</t>
+          <t>124550</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>78487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104205</t>
+          <t>103855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175867</t>
+          <t>177338</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>221118</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>324928</t>
+          <t>325274</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>369370</t>
+          <t>368016</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>310267</t>
+          <t>311293</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>344613</t>
+          <t>344953</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>647736</t>
+          <t>647221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>703966</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89281</t>
+          <t>92005</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126709</t>
+          <t>126276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113998</t>
+          <t>113735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144460</t>
+          <t>142660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214134</t>
+          <t>212066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>259110</t>
+          <t>261472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>53574</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>77016</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78204</t>
+          <t>78842</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58384</t>
+          <t>60052</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147482</t>
+          <t>150938</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>169997</t>
+          <t>169840</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>201273</t>
+          <t>198987</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238648</t>
+          <t>240845</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>516231</t>
+          <t>509390</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>432729</t>
+          <t>428915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>743981</t>
+          <t>752974</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103955</t>
+          <t>103391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132876</t>
+          <t>131884</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69400</t>
+          <t>74733</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>291966</t>
+          <t>288146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>167195</t>
+          <t>152066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>395458</t>
+          <t>397642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>31915</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52591</t>
+          <t>52676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76232</t>
+          <t>76948</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76809</t>
+          <t>77288</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>101264</t>
+          <t>103429</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77078</t>
+          <t>77592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>100100</t>
+          <t>101616</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>162372</t>
+          <t>161505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>196078</t>
+          <t>196039</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>137828</t>
+          <t>137488</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163668</t>
+          <t>164846</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>299744</t>
+          <t>298297</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>325578</t>
+          <t>324207</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>444492</t>
+          <t>445836</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>480944</t>
+          <t>483535</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>501443</t>
+          <t>506288</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>718854</t>
+          <t>714052</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>540195</t>
+          <t>534566</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>721328</t>
+          <t>724014</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1124701</t>
+          <t>1142504</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1416665</t>
+          <t>1412003</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2184617</t>
+          <t>2180364</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2548430</t>
+          <t>2546506</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2118079</t>
+          <t>2123130</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2504404</t>
+          <t>2513248</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,47 +15737,47 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>4528150</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>4342465</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>4870359</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>63,73%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>68,54%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>4528150</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>4338019</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>4883446</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>400712</t>
+          <t>400690</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>570666</t>
+          <t>574038</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>612161</t>
+          <t>616359</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>826788</t>
+          <t>820730</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1092163</t>
+          <t>1099221</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1366081</t>
+          <t>1372437</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ESTUDIOS-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>60068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67190</t>
+          <t>64514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100241</t>
+          <t>100608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357365</t>
+          <t>357950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394532</t>
+          <t>394635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336953</t>
+          <t>339572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373194</t>
+          <t>373036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706751</t>
+          <t>708124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758465</t>
+          <t>758800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>66655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99868</t>
+          <t>100034</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79736</t>
+          <t>79823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126184</t>
+          <t>124805</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>169346</t>
+          <t>167762</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170020</t>
+          <t>170510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>218843</t>
+          <t>220753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163213</t>
+          <t>159161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208660</t>
+          <t>206431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346960</t>
+          <t>344027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410428</t>
+          <t>410495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>425093</t>
+          <t>425937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>481745</t>
+          <t>480274</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>349616</t>
+          <t>351791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>400970</t>
+          <t>399693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>791615</t>
+          <t>791699</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>865421</t>
+          <t>864951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>72867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107863</t>
+          <t>107205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51401</t>
+          <t>51664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83000</t>
+          <t>84415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130217</t>
+          <t>130485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180117</t>
+          <t>178328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120108</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162046</t>
+          <t>159983</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108714</t>
+          <t>110297</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154457</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>237364</t>
+          <t>235148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>295850</t>
+          <t>294495</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>352038</t>
+          <t>349301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>401299</t>
+          <t>397311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>401178</t>
+          <t>397865</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>453383</t>
+          <t>450950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>767364</t>
+          <t>767957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>840909</t>
+          <t>840676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103205</t>
+          <t>107435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143480</t>
+          <t>148324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113374</t>
+          <t>114486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154030</t>
+          <t>155391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230392</t>
+          <t>231638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291376</t>
+          <t>289745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83148</t>
+          <t>82767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120034</t>
+          <t>120089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46502</t>
+          <t>45230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75408</t>
+          <t>75298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139487</t>
+          <t>135464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183975</t>
+          <t>184077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245592</t>
+          <t>245733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291635</t>
+          <t>292457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>240355</t>
+          <t>239631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>283475</t>
+          <t>284521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>498621</t>
+          <t>498792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>563433</t>
+          <t>564891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129952</t>
+          <t>128855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172360</t>
+          <t>171674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>174178</t>
+          <t>171695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216500</t>
+          <t>215365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>310084</t>
+          <t>315682</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>376674</t>
+          <t>375942</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58763</t>
+          <t>57995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>57325</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90125</t>
+          <t>91260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>108630</t>
+          <t>112435</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>147936</t>
+          <t>149237</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86610</t>
+          <t>84950</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>121628</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>210525</t>
+          <t>207434</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261391</t>
+          <t>260489</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193198</t>
+          <t>193992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232488</t>
+          <t>233136</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>249951</t>
+          <t>251598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287216</t>
+          <t>289649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>455208</t>
+          <t>454366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>510494</t>
+          <t>509181</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33045</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61626</t>
+          <t>61421</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48399</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75969</t>
+          <t>76285</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>32487</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>55702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88157</t>
+          <t>87071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123775</t>
+          <t>125137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>186004</t>
+          <t>186680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>217188</t>
+          <t>218773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>267987</t>
+          <t>268673</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>295231</t>
+          <t>295275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>464548</t>
+          <t>463508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>505348</t>
+          <t>506103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17620</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>34019</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>157434</t>
+          <t>157841</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180756</t>
+          <t>179958</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>291469</t>
+          <t>292200</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>315380</t>
+          <t>314458</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>457607</t>
+          <t>457306</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>490837</t>
+          <t>490416</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>509292</t>
+          <t>510725</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>600239</t>
+          <t>598849</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>438952</t>
+          <t>439315</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>516263</t>
+          <t>520038</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>966748</t>
+          <t>972865</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1094736</t>
+          <t>1087365</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1627685</t>
+          <t>1634483</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1750356</t>
+          <t>1749045</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1530722</t>
+          <t>1526643</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1646221</t>
+          <t>1645457</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3194336</t>
+          <t>3202345</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3362410</t>
+          <t>3360901</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>983225</t>
+          <t>981453</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1088008</t>
+          <t>1084128</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1252523</t>
+          <t>1259040</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1367276</t>
+          <t>1371631</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2259779</t>
+          <t>2270234</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2412654</t>
+          <t>2424643</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25681</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39316</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66416</t>
+          <t>67201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>55283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86347</t>
+          <t>88648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363795</t>
+          <t>363462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>396740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322136</t>
+          <t>321336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>356569</t>
+          <t>355952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697719</t>
+          <t>696260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744859</t>
+          <t>743705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43339</t>
+          <t>42177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71350</t>
+          <t>71032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50685</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76313</t>
+          <t>76864</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114428</t>
+          <t>113682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149939</t>
+          <t>148416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>195029</t>
+          <t>196426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146897</t>
+          <t>146143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190481</t>
+          <t>190876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309366</t>
+          <t>308369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376496</t>
+          <t>374606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>421187</t>
+          <t>421316</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>472733</t>
+          <t>471170</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>346021</t>
+          <t>346650</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>395803</t>
+          <t>395879</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>779992</t>
+          <t>778378</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>854189</t>
+          <t>850060</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82456</t>
+          <t>83614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54349</t>
+          <t>54674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87994</t>
+          <t>87645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114568</t>
+          <t>113687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160283</t>
+          <t>162117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96537</t>
+          <t>97334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138188</t>
+          <t>139671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94539</t>
+          <t>94139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134208</t>
+          <t>135479</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>199391</t>
+          <t>198930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>259508</t>
+          <t>258517</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>420570</t>
+          <t>423040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>474481</t>
+          <t>474747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>432980</t>
+          <t>432097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>484332</t>
+          <t>485065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>871213</t>
+          <t>872727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>946507</t>
+          <t>948271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94938</t>
+          <t>91832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137438</t>
+          <t>131891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118551</t>
+          <t>120274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162064</t>
+          <t>164401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224555</t>
+          <t>224898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284327</t>
+          <t>281532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89057</t>
+          <t>87792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129994</t>
+          <t>129700</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70854</t>
+          <t>70762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110527</t>
+          <t>107858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>169625</t>
+          <t>169907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226859</t>
+          <t>225104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>346105</t>
+          <t>341802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>396637</t>
+          <t>394828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>312037</t>
+          <t>311535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>364025</t>
+          <t>362870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>669041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>744646</t>
+          <t>744783</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,51%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115944</t>
+          <t>115814</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158420</t>
+          <t>161130</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165677</t>
+          <t>169201</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214601</t>
+          <t>214735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>296351</t>
+          <t>292561</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>358605</t>
+          <t>358878</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>28338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>54558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42069</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74518</t>
+          <t>73572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>175520</t>
+          <t>176882</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>221176</t>
+          <t>219105</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>146057</t>
+          <t>145764</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188508</t>
+          <t>188436</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>336056</t>
+          <t>334709</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>397121</t>
+          <t>394826</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167463</t>
+          <t>168536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210706</t>
+          <t>211058</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>241509</t>
+          <t>242518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>286279</t>
+          <t>286516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418290</t>
+          <t>424210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>481146</t>
+          <t>485308</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25122</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>53526</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67695</t>
+          <t>68752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100951</t>
+          <t>101376</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41295</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69406</t>
+          <t>69988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118621</t>
+          <t>118485</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162682</t>
+          <t>161898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>185471</t>
+          <t>185610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>222044</t>
+          <t>220484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268532</t>
+          <t>266389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>299711</t>
+          <t>297290</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>460837</t>
+          <t>462979</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>509807</t>
+          <t>510618</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48078</t>
+          <t>48736</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39939</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46845</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>80207</t>
+          <t>82146</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>197851</t>
+          <t>196638</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>221852</t>
+          <t>221638</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>337131</t>
+          <t>337013</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>362148</t>
+          <t>361114</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>542708</t>
+          <t>539683</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>577003</t>
+          <t>575752</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>441643</t>
+          <t>440170</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>524800</t>
+          <t>520178</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>416935</t>
+          <t>419779</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>497515</t>
+          <t>500177</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>883662</t>
+          <t>881610</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1003061</t>
+          <t>1002585</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1904778</t>
+          <t>1903962</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2023077</t>
+          <t>2025145</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1699465</t>
+          <t>1696572</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1818182</t>
+          <t>1822178</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3635571</t>
+          <t>3632840</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3806724</t>
+          <t>3810155</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>919538</t>
+          <t>918790</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1034254</t>
+          <t>1028475</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1276796</t>
+          <t>1272847</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1394574</t>
+          <t>1397965</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2228586</t>
+          <t>2232955</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2393811</t>
+          <t>2397915</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55217</t>
+          <t>56755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58224</t>
+          <t>59325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70314</t>
+          <t>70777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106488</t>
+          <t>106269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326616</t>
+          <t>328558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358171</t>
+          <t>358723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308418</t>
+          <t>307098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337607</t>
+          <t>336467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>645415</t>
+          <t>646062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>688910</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>40399</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>69999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112547</t>
+          <t>112879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155201</t>
+          <t>154354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142952</t>
+          <t>142437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184302</t>
+          <t>184304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267042</t>
+          <t>269003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324077</t>
+          <t>328984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>364356</t>
+          <t>363771</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>411182</t>
+          <t>408410</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>331501</t>
+          <t>330225</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377051</t>
+          <t>375114</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>709320</t>
+          <t>708069</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>771855</t>
+          <t>771470</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48999</t>
+          <t>50309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82511</t>
+          <t>81957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32993</t>
+          <t>33420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60309</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92680</t>
+          <t>93043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132107</t>
+          <t>132206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130980</t>
+          <t>129833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>176377</t>
+          <t>176124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136720</t>
+          <t>136268</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182200</t>
+          <t>178587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>282433</t>
+          <t>278350</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>340515</t>
+          <t>339991</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>409936</t>
+          <t>409980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>461621</t>
+          <t>461879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>412854</t>
+          <t>413522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>459356</t>
+          <t>461162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>836788</t>
+          <t>839128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>904797</t>
+          <t>906301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63837</t>
+          <t>64136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96574</t>
+          <t>96019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49413</t>
+          <t>50386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78725</t>
+          <t>80210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119734</t>
+          <t>122446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165082</t>
+          <t>165695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80737</t>
+          <t>80617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120293</t>
+          <t>120058</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86779</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125121</t>
+          <t>123190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>175814</t>
+          <t>176993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231057</t>
+          <t>233647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429780</t>
+          <t>429253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>477438</t>
+          <t>476588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>390196</t>
+          <t>394813</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439490</t>
+          <t>442228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835689</t>
+          <t>833934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>907985</t>
+          <t>905917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74074</t>
+          <t>74015</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110236</t>
+          <t>110714</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>104934</t>
+          <t>104650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146570</t>
+          <t>146726</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189412</t>
+          <t>191597</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>246079</t>
+          <t>245632</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64124</t>
+          <t>64328</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99078</t>
+          <t>99874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59422</t>
+          <t>60084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102572</t>
+          <t>104072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148974</t>
+          <t>150143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>236712</t>
+          <t>238831</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>281784</t>
+          <t>283599</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>247202</t>
+          <t>247212</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>292522</t>
+          <t>292933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>495786</t>
+          <t>497167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>560423</t>
+          <t>563581</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>116482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157993</t>
+          <t>156824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159124</t>
+          <t>159365</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203579</t>
+          <t>201432</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>286458</t>
+          <t>286338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>348725</t>
+          <t>346679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19788</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42422</t>
+          <t>42876</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>35665</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>39891</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68742</t>
+          <t>69726</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116958</t>
+          <t>116343</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153407</t>
+          <t>151748</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99018</t>
+          <t>96339</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135312</t>
+          <t>134268</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223869</t>
+          <t>223881</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>276309</t>
+          <t>276306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>149710</t>
+          <t>151833</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186742</t>
+          <t>186034</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>218122</t>
+          <t>219141</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>257575</t>
+          <t>259131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>379888</t>
+          <t>381802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>434065</t>
+          <t>435495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35422</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47521</t>
+          <t>46678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71775</t>
+          <t>70495</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53220</t>
+          <t>55133</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90817</t>
+          <t>92311</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>110328</t>
+          <t>110569</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>154192</t>
+          <t>154048</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>171384</t>
+          <t>170607</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>197451</t>
+          <t>196183</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>295282</t>
+          <t>295671</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>337115</t>
+          <t>333465</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>475738</t>
+          <t>474910</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>522919</t>
+          <t>522902</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>505598</t>
+          <t>502448</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>592706</t>
+          <t>591218</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>503545</t>
+          <t>507561</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>590770</t>
+          <t>591602</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1043913</t>
+          <t>1036004</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1163837</t>
+          <t>1166070</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2019681</t>
+          <t>2011761</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2137122</t>
+          <t>2133059</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1927529</t>
+          <t>1927905</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2048841</t>
+          <t>2050732</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3989228</t>
+          <t>3980850</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4149508</t>
+          <t>4147983</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>701210</t>
+          <t>704061</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>799716</t>
+          <t>805964</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>939460</t>
+          <t>939649</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1053606</t>
+          <t>1052867</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1675399</t>
+          <t>1678934</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1818983</t>
+          <t>1823928</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>39372</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>25912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53510</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40724</t>
+          <t>47302</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>32838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58124</t>
+          <t>68269</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75772</t>
+          <t>86674</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56402</t>
+          <t>64459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102281</t>
+          <t>111415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>352742</t>
+          <t>348556</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>331448</t>
+          <t>324543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>370172</t>
+          <t>366781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>259932</t>
+          <t>301828</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240493</t>
+          <t>280768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275463</t>
+          <t>319050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>612673</t>
+          <t>650384</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583732</t>
+          <t>621533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635880</t>
+          <t>675737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29263</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25588</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>33248</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>55299</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92405</t>
+          <t>103901</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69549</t>
+          <t>81402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115268</t>
+          <t>130320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>142232</t>
+          <t>150807</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89099</t>
+          <t>127886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174413</t>
+          <t>171679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>234637</t>
+          <t>254708</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177236</t>
+          <t>225071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>268535</t>
+          <t>290487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>296327</t>
+          <t>332023</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>269934</t>
+          <t>304611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>320040</t>
+          <t>356612</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>353205</t>
+          <t>328808</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>318919</t>
+          <t>305860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>413984</t>
+          <t>351077</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>649532</t>
+          <t>660831</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>611128</t>
+          <t>625092</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>715996</t>
+          <t>694273</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33469</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>59950</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34348</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70153</t>
+          <t>77121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>422201</t>
+          <t>474406</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422201</t>
+          <t>474406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422201</t>
+          <t>474406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>933705</t>
+          <t>975489</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933705</t>
+          <t>975489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933705</t>
+          <t>975489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>144829</t>
+          <t>164525</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126446</t>
+          <t>139494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167457</t>
+          <t>187834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>147013</t>
+          <t>167883</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>128841</t>
+          <t>150152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163207</t>
+          <t>187992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>291841</t>
+          <t>332408</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>266686</t>
+          <t>303614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321273</t>
+          <t>365950</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>352349</t>
+          <t>400859</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328999</t>
+          <t>374868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373354</t>
+          <t>426081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>365932</t>
+          <t>417625</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>348556</t>
+          <t>396325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>384406</t>
+          <t>436585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>718279</t>
+          <t>818484</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>688572</t>
+          <t>787759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745477</t>
+          <t>848992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38832</t>
+          <t>53157</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>40988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>69321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>26485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39215</t>
+          <t>48270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>68190</t>
+          <t>89234</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53120</t>
+          <t>72611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82333</t>
+          <t>108111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536010</t>
+          <t>618541</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536010</t>
+          <t>618541</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536010</t>
+          <t>618541</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>542302</t>
+          <t>621585</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>542302</t>
+          <t>621585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>542302</t>
+          <t>621585</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1078311</t>
+          <t>1240126</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1078311</t>
+          <t>1240126</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1078311</t>
+          <t>1240126</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>162137</t>
+          <t>166870</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67598</t>
+          <t>145249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234496</t>
+          <t>190408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>168302</t>
+          <t>182327</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140521</t>
+          <t>165801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187540</t>
+          <t>200915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>330439</t>
+          <t>349196</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213780</t>
+          <t>318220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>403660</t>
+          <t>379570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>668362</t>
+          <t>468456</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>573172</t>
+          <t>439530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>792695</t>
+          <t>491911</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>475122</t>
+          <t>482894</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451791</t>
+          <t>461763</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>512688</t>
+          <t>502311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1143484</t>
+          <t>951350</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1045657</t>
+          <t>920394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1312225</t>
+          <t>985290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>68,77%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82343</t>
+          <t>79548</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68391</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54480</t>
+          <t>59257</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88385</t>
+          <t>84916</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>122118</t>
+          <t>132182</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74982</t>
+          <t>113981</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156803</t>
+          <t>152574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>884225</t>
+          <t>696908</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>884225</t>
+          <t>696908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>884225</t>
+          <t>696908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735820</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735820</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1596040</t>
+          <t>1432728</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1596040</t>
+          <t>1432728</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1596040</t>
+          <t>1432728</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>107218</t>
+          <t>118038</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90706</t>
+          <t>101454</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124550</t>
+          <t>137717</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>90458</t>
+          <t>103272</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78487</t>
+          <t>89773</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103855</t>
+          <t>117659</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>197676</t>
+          <t>221310</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177338</t>
+          <t>197194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221118</t>
+          <t>244969</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>346545</t>
+          <t>375960</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>325274</t>
+          <t>352418</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368016</t>
+          <t>397922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>327894</t>
+          <t>362590</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>311293</t>
+          <t>344321</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>344953</t>
+          <t>381511</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>674439</t>
+          <t>738551</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>647221</t>
+          <t>708618</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>768490</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>107471</t>
+          <t>115348</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92005</t>
+          <t>98563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126276</t>
+          <t>135299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>128414</t>
+          <t>141730</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113735</t>
+          <t>126755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142660</t>
+          <t>158923</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>235885</t>
+          <t>257079</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>212066</t>
+          <t>232318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261472</t>
+          <t>283976</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546767</t>
+          <t>607593</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546767</t>
+          <t>607593</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546767</t>
+          <t>607593</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1108000</t>
+          <t>1216940</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1108000</t>
+          <t>1216940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1108000</t>
+          <t>1216940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63804</t>
+          <t>72318</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>60894</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77016</t>
+          <t>85279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>49149</t>
+          <t>55875</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>46041</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78842</t>
+          <t>66345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112953</t>
+          <t>128194</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60052</t>
+          <t>112833</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>150938</t>
+          <t>146043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>184524</t>
+          <t>205600</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>169840</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198987</t>
+          <t>220761</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>367000</t>
+          <t>179138</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240845</t>
+          <t>164088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>509390</t>
+          <t>193795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>551524</t>
+          <t>384739</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>428915</t>
+          <t>359491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>752974</t>
+          <t>406680</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>117937</t>
+          <t>127039</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>111387</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131884</t>
+          <t>143278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>188313</t>
+          <t>202250</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74733</t>
+          <t>185876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>288146</t>
+          <t>216047</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>306250</t>
+          <t>329289</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152066</t>
+          <t>308107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>397642</t>
+          <t>352167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,81%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>366266</t>
+          <t>404957</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>366266</t>
+          <t>404957</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>366266</t>
+          <t>404957</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>604461</t>
+          <t>437263</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>604461</t>
+          <t>437263</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>604461</t>
+          <t>437263</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>970727</t>
+          <t>842221</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>970727</t>
+          <t>842221</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>970727</t>
+          <t>842221</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>27412</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>73974</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52676</t>
+          <t>62453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76948</t>
+          <t>87644</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>85338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>103429</t>
+          <t>112481</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>88739</t>
+          <t>98507</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77592</t>
+          <t>86603</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>101616</t>
+          <t>112122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>178218</t>
+          <t>197619</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>161505</t>
+          <t>179170</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>196039</t>
+          <t>216889</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>151306</t>
+          <t>163057</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>137488</t>
+          <t>148810</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>164846</t>
+          <t>178924</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>312420</t>
+          <t>336531</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>298297</t>
+          <t>322255</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>324207</t>
+          <t>349742</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>463727</t>
+          <t>499588</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>445836</t>
+          <t>477056</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>483535</t>
+          <t>520912</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>281966</t>
+          <t>308731</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>281966</t>
+          <t>308731</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>281966</t>
+          <t>308731</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>423745</t>
+          <t>462450</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>423745</t>
+          <t>462450</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>423745</t>
+          <t>462450</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>705712</t>
+          <t>771181</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>705712</t>
+          <t>771181</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>705712</t>
+          <t>771181</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>506288</t>
+          <t>657160</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>714052</t>
+          <t>764457</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>534566</t>
+          <t>693606</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>724014</t>
+          <t>780144</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1142504</t>
+          <t>1381434</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1412003</t>
+          <t>1517799</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2180364</t>
+          <t>2169774</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2546506</t>
+          <t>2296031</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2123130</t>
+          <t>2119928</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2513248</t>
+          <t>2227481</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401958</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4342465</t>
+          <t>4321951</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4870359</t>
+          <t>4480650</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>400690</t>
+          <t>535058</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>574038</t>
+          <t>623416</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>616359</t>
+          <t>777850</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>820730</t>
+          <t>863139</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1099221</t>
+          <t>1341891</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1372437</t>
+          <t>1457889</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
